--- a/reports/devops-juniors-israel-2026-W30.xlsx
+++ b/reports/devops-juniors-israel-2026-W30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="382">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-20T09:33:36</t>
+    <t xml:space="preserve">2026-07-21T08:43:22</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -199,145 +199,172 @@
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps &amp; Data Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Azure, Cloud (any), Git, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-data-platform-engineer-at-extreme-4442586276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
     <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps &amp; Data Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Azure, Cloud (any), Git, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-data-platform-engineer-at-extreme-4442586276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineer, Software Development, Graviton Team</t>
@@ -352,7 +379,7 @@
     <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4416059820</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4443042450</t>
   </si>
   <si>
     <t xml:space="preserve">Log-On Software</t>
@@ -394,64 +421,58 @@
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-at-shavit-software-4442576674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-reline-it-solutions-4438417196</t>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
   </si>
   <si>
     <t xml:space="preserve">ZyG</t>
@@ -463,361 +484,385 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
   </si>
   <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4441499292</t>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator (25278)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-25278-at-yael-group-4438052676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Science Student for AI Solutions Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-science-student-for-ai-solutions-group-at-intel-4439417170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiberias, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MatchPointIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-matchpointit-4440116701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4418374586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4417221824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-17</t>
   </si>
   <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science Student for AI Solutions Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-science-student-for-ai-solutions-group-at-intel-4439417170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiberias, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4418374586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4417221824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELP DESK TIER ONE 241758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-one-241758-at-experis-4439208565</t>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk (Temporary)</t>
@@ -838,30 +883,6 @@
     <t xml:space="preserve">2026-06-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
     <t xml:space="preserve">RealPlay</t>
   </si>
   <si>
@@ -871,189 +892,129 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Infrastructure &amp; Support Specialist (Tier 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-support-specialist-tier-2-at-moveo-source-4434338174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galooli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-technical-support-specialist-at-galooli-4432181954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+    <t xml:space="preserve">IT Support Technician (36735)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-36735-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442595551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4440105972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-philips-4433612673</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Technician</t>
   </si>
   <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-Site Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LabOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
+    <t xml:space="preserve">Accel Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-accel-solutions-4439663778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-philips-4433612673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-accel-solutions-4439663778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
     <t xml:space="preserve">Help Desk טכנאי/ת</t>
   </si>
   <si>
@@ -1069,39 +1030,30 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
   </si>
   <si>
-    <t xml:space="preserve">תמיכה טכנית - מערכת Meteor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StoreNext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%9E%D7%A2%D7%A8%D7%9B%D7%AA-meteor-at-storenext-4440240961</t>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
   </si>
   <si>
     <t xml:space="preserve">Oktopost</t>
   </si>
   <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">סטודנט.ית למשרת אבטחת מידע - ניהול מערכות מידע ביחידת הביטחון</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rafael Advanced Defense Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karmiel, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%A1%D7%98%D7%95%D7%93%D7%A0%D7%98-%D7%99%D7%AA-%D7%9C%D7%9E%D7%A9%D7%A8%D7%AA-%D7%90%D7%91%D7%98%D7%97%D7%AA-%D7%9E%D7%99%D7%93%D7%A2-%D7%A0%D7%99%D7%94%D7%95%D7%9C-%D7%9E%D7%A2%D7%A8%D7%9B%D7%95%D7%AA-%D7%9E%D7%99%D7%93%D7%A2-%D7%91%D7%99%D7%97%D7%99%D7%93%D7%AA-%D7%94%D7%91%D7%99%D7%98%D7%97%D7%95%D7%9F-at-rafael-advanced-defense-systems-4437157621</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1111,39 +1063,39 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
@@ -1171,7 +1123,10 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1202,9 +1157,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
   <si>
     <t xml:space="preserve">remoteok</t>
@@ -1332,7 +1284,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -1340,7 +1292,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1348,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -1356,7 +1308,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10">
@@ -1438,7 +1390,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
@@ -1446,7 +1398,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1462,7 +1414,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1488,7 +1440,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
@@ -1683,31 +1635,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1715,31 +1667,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1747,19 +1699,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>80</v>
@@ -1782,10 +1734,10 @@
         <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1794,16 +1746,16 @@
         <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1811,13 +1763,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1826,16 +1778,16 @@
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -1843,13 +1795,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>28</v>
@@ -1858,16 +1810,16 @@
         <v>67</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -1875,13 +1827,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>29</v>
@@ -1890,16 +1842,16 @@
         <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -1907,13 +1859,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
@@ -1922,16 +1874,16 @@
         <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1939,31 +1891,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -1971,19 +1923,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>114</v>
@@ -1995,7 +1947,7 @@
         <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16">
@@ -2003,31 +1955,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -2035,19 +1987,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>123</v>
@@ -2059,7 +2011,7 @@
         <v>124</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -2067,13 +2019,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -2082,16 +2034,16 @@
         <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -2099,25 +2051,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>132</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>133</v>
@@ -2131,31 +2083,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
         <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
@@ -2163,10 +2115,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>51</v>
@@ -2178,16 +2130,16 @@
         <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22">
@@ -2195,31 +2147,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23">
@@ -2227,13 +2179,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -2242,16 +2194,16 @@
         <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24">
@@ -2259,31 +2211,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>153</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -2294,10 +2246,10 @@
         <v>60</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>26</v>
@@ -2306,16 +2258,16 @@
         <v>32</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26">
@@ -2323,31 +2275,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2400,7 +2352,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2415,22 +2367,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
@@ -2453,7 +2405,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2465,7 +2417,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -2488,7 +2440,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2500,7 +2452,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -2523,7 +2475,7 @@
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2535,7 +2487,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
@@ -2558,7 +2510,7 @@
         <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2570,100 +2522,100 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
         <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2675,7 +2627,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2683,10 +2635,10 @@
         <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2695,33 +2647,33 @@
         <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K9" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2730,33 +2682,33 @@
         <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="K10" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>28</v>
@@ -2765,33 +2717,33 @@
         <v>67</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>29</v>
@@ -2800,33 +2752,33 @@
         <v>57</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="K12" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
@@ -2835,80 +2787,80 @@
         <v>56</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="K13" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
         <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
@@ -2917,68 +2869,68 @@
         <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="K16" s="3">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
@@ -2987,21 +2939,21 @@
         <v>124</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="K17" s="3">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
@@ -3010,48 +2962,48 @@
         <v>47</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K18" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>132</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>133</v>
@@ -3060,50 +3012,50 @@
         <v>134</v>
       </c>
       <c r="K19" s="3">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
         <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>51</v>
@@ -3115,68 +3067,68 @@
         <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K21" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -3185,57 +3137,57 @@
         <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>150</v>
+        <v>74</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="K24" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -3243,10 +3195,10 @@
         <v>60</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>26</v>
@@ -3255,150 +3207,150 @@
         <v>32</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K25" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="K26" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="K27" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>30</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K28" s="3">
         <v>27</v>
-      </c>
-      <c r="E28" s="3">
-        <v>26</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K28" s="3">
-        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>182</v>
+        <v>74</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>183</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
@@ -3407,45 +3359,45 @@
         <v>184</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="K29" s="3">
-        <v>66</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="K30" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3456,31 +3408,31 @@
         <v>191</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>122</v>
+        <v>192</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="K31" s="3">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -3491,31 +3443,31 @@
         <v>196</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
+        <v>23</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K32" s="3">
         <v>20</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K32" s="3">
-        <v>66</v>
       </c>
     </row>
     <row r="33">
@@ -3526,124 +3478,124 @@
         <v>201</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
         <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="K35" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>20</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>17</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="G36" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
@@ -3652,7 +3604,7 @@
         <v>220</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>205</v>
+        <v>65</v>
       </c>
       <c r="K36" s="3">
         <v>1</v>
@@ -3663,10 +3615,10 @@
         <v>221</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3675,103 +3627,103 @@
         <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="K37" s="3">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>17</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="3">
-        <v>16</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="G38" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="K38" s="3">
-        <v>66</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="K39" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>27</v>
@@ -3780,68 +3732,68 @@
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K40" s="3">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E41" s="3">
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="K41" s="3">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3850,92 +3802,92 @@
         <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K42" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>66</v>
+        <v>251</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3">
+        <v>13</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K43" s="3">
         <v>12</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>60</v>
+        <v>255</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -3943,10 +3895,10 @@
         <v>60</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>26</v>
@@ -3955,33 +3907,33 @@
         <v>12</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>224</v>
+        <v>60</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>26</v>
@@ -3990,68 +3942,68 @@
         <v>12</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K47" s="3">
-        <v>57</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>104</v>
+        <v>271</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -4060,33 +4012,33 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="K48" s="3">
-        <v>3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4095,33 +4047,33 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>205</v>
+        <v>278</v>
       </c>
       <c r="K49" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>270</v>
+        <v>74</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4130,33 +4082,33 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="K50" s="3">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4165,33 +4117,33 @@
         <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="K51" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>278</v>
+        <v>72</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4200,33 +4152,33 @@
         <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>281</v>
+        <v>59</v>
       </c>
       <c r="K52" s="3">
-        <v>15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4235,488 +4187,488 @@
         <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K53" s="3">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>285</v>
+        <v>245</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>189</v>
+        <v>297</v>
       </c>
       <c r="K54" s="3">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>292</v>
+        <v>134</v>
       </c>
       <c r="K55" s="3">
-        <v>10</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>235</v>
+        <v>122</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>294</v>
+        <v>233</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>295</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="K56" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="K57" s="3">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>181</v>
+        <v>309</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>182</v>
+        <v>310</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>304</v>
+        <v>65</v>
       </c>
       <c r="K58" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>122</v>
+        <v>310</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E59" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>125</v>
+        <v>316</v>
       </c>
       <c r="K59" s="3">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>67</v>
+        <v>318</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E60" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="K60" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>315</v>
+        <v>119</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E61" s="3">
         <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="K61" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="D62" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>320</v>
+        <v>131</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>326</v>
+        <v>185</v>
       </c>
       <c r="K63" s="3">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>328</v>
+        <v>217</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E64" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K64" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>224</v>
+        <v>325</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>332</v>
+        <v>233</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>70</v>
+        <v>185</v>
       </c>
       <c r="K65" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="K66" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>297</v>
+        <v>200</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>332</v>
+        <v>74</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
@@ -4725,267 +4677,59 @@
         <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="K67" s="3">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>342</v>
+        <v>176</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>343</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E68" s="3">
-        <v>3</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>329</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>169</v>
+        <v>344</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>345</v>
+        <v>65</v>
       </c>
       <c r="K68" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69" s="3">
-        <v>3</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K69" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="K70" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="3">
-        <v>3</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="K71" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E73" s="3">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K73" s="3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E74" s="3">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K74" s="3">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K74"/>
+  <autoFilter ref="A1:K68"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5054,12 +4798,6 @@
     <hyperlink ref="I66" r:id="rId65"/>
     <hyperlink ref="I67" r:id="rId66"/>
     <hyperlink ref="I68" r:id="rId67"/>
-    <hyperlink ref="I69" r:id="rId68"/>
-    <hyperlink ref="I70" r:id="rId69"/>
-    <hyperlink ref="I71" r:id="rId70"/>
-    <hyperlink ref="I72" r:id="rId71"/>
-    <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5067,8 +4805,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -5090,10 +4828,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -5101,418 +4839,167 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>114</v>
+        <v>188</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>28</v>
+        <v>245</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>135</v>
+        <v>246</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>136</v>
+        <v>248</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>137</v>
+        <v>249</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>292</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>142</v>
+        <v>293</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>144</v>
+        <v>276</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>145</v>
+        <v>294</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>147</v>
+        <v>295</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>148</v>
+        <v>302</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3">
-        <v>20</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="3">
-        <v>12</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="3">
-        <v>12</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="3">
-        <v>12</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="3">
-        <v>12</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="3">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="3">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="3">
-        <v>4</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="3">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="3">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G19"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5521,17 +5008,6 @@
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
-    <hyperlink ref="F13" r:id="rId12"/>
-    <hyperlink ref="F14" r:id="rId13"/>
-    <hyperlink ref="F15" r:id="rId14"/>
-    <hyperlink ref="F16" r:id="rId15"/>
-    <hyperlink ref="F17" r:id="rId16"/>
-    <hyperlink ref="F18" r:id="rId17"/>
-    <hyperlink ref="F19" r:id="rId18"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5546,178 +5022,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B2" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B3" s="3">
         <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B4" s="3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>232</v>
+        <v>311</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>321</v>
+        <v>239</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="B10" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="B11" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -5737,10 +5213,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2">
@@ -5748,10 +5224,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3">
@@ -5759,10 +5235,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4">
@@ -5773,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5">
@@ -5781,10 +5257,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6">
@@ -5795,7 +5271,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -5816,13 +5292,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
@@ -5833,7 +5309,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>396</v>
+        <v>344</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5842,22 +5318,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>396</v>
+        <v>344</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>396</v>
+        <v>344</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W30.xlsx
+++ b/reports/devops-juniors-israel-2026-W30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-21T08:43:22</t>
+    <t xml:space="preserve">2026-07-22T08:42:43</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -100,12 +100,12 @@
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -196,6 +196,24 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
@@ -214,949 +232,895 @@
     <t xml:space="preserve">2026-07-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+    <t xml:space="preserve">MER Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2 - 240769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-240769-at-experis-israel-4434811963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salvador Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-support-engineer-at-salvador-technologies-4440494256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiberias, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps &amp; Data Platform Engineer</t>
+    <t xml:space="preserve">Help Desk Specialist</t>
   </si>
   <si>
     <t xml:space="preserve">Extreme</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Azure, Cloud (any), Git, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-data-platform-engineer-at-extreme-4442586276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NLPearl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-nlpearl-4440427593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Customer Support Rep- Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-customer-support-rep-student-at-bright-data-4440677972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
   </si>
   <si>
     <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer, Software Development, Graviton Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4443042450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Monitoring, Databases, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-at-log-on-software-4440128123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician (36735)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-36735-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442595551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-31</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (25278)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-25278-at-yael-group-4438052676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science Student for AI Solutions Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-science-student-for-ai-solutions-group-at-intel-4439417170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiberias, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MatchPointIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-matchpointit-4440116701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tnuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoreNext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accel Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-accel-solutions-4439663778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
   </si>
   <si>
     <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
   </si>
   <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4418374586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4417221824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician (36735)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-36735-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442595551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4440105972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4443762238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-philips-4433612673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-accel-solutions-4439663778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk טכנאי/ת</t>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-genie-4438491899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">remoteok</t>
@@ -1284,7 +1248,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -1300,7 +1264,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1308,7 +1272,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>512</v>
+        <v>519</v>
       </c>
     </row>
     <row r="10">
@@ -1390,7 +1354,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -1398,7 +1362,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1406,7 +1370,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1414,7 +1378,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1422,7 +1386,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1440,7 +1404,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
@@ -1448,7 +1412,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1516,7 +1480,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1548,7 +1512,7 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1612,10 +1576,10 @@
         <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>63</v>
@@ -1644,10 +1608,10 @@
         <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>69</v>
@@ -1667,31 +1631,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>76</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>74</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1699,19 +1663,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3">
         <v>74</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="3">
-        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>80</v>
@@ -1734,10 +1698,10 @@
         <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1746,16 +1710,16 @@
         <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1763,13 +1727,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1778,16 +1742,16 @@
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -1795,28 +1759,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>65</v>
@@ -1827,31 +1791,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" s="3">
         <v>57</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -1859,31 +1823,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1891,31 +1855,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -1923,31 +1887,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -1955,31 +1919,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -1987,31 +1951,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
@@ -2019,31 +1983,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -2051,31 +2015,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20">
@@ -2083,31 +2047,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -2115,31 +2079,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22">
@@ -2147,31 +2111,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
@@ -2179,31 +2143,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24">
@@ -2211,31 +2175,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25">
@@ -2243,31 +2207,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26">
@@ -2275,31 +2239,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>82</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2352,7 +2316,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2367,22 +2331,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
@@ -2396,7 +2360,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2405,7 +2369,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2417,7 +2381,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -2431,7 +2395,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2440,7 +2404,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2452,7 +2416,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -2475,7 +2439,7 @@
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2487,7 +2451,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -2501,16 +2465,16 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2522,7 +2486,7 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2536,16 +2500,16 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2557,65 +2521,65 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>76</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>74</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3">
         <v>74</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="3">
-        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2627,7 +2591,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -2635,10 +2599,10 @@
         <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2647,33 +2611,33 @@
         <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2682,159 +2646,159 @@
         <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K10" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3">
         <v>57</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K12" s="3">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
         <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K14" s="3">
         <v>22</v>
@@ -2842,734 +2806,734 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K15" s="3">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="K17" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="K18" s="3">
-        <v>67</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K19" s="3">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="K20" s="3">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K21" s="3">
-        <v>14</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="K22" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K23" s="3">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="K24" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="K25" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="K27" s="3">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="K28" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>61</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="K29" s="3">
-        <v>8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>192</v>
+        <v>143</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="K31" s="3">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>74</v>
+        <v>201</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="K32" s="3">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>131</v>
+        <v>206</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="K33" s="3">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
         <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="K34" s="3">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
         <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>215</v>
+        <v>71</v>
       </c>
       <c r="K35" s="3">
         <v>2</v>
@@ -3577,48 +3541,48 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>65</v>
+        <v>224</v>
       </c>
       <c r="K36" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3627,33 +3591,33 @@
         <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>226</v>
+        <v>166</v>
       </c>
       <c r="K37" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>228</v>
+        <v>61</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>229</v>
+        <v>62</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3662,138 +3626,138 @@
         <v>17</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="K38" s="3">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E39" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>105</v>
+        <v>238</v>
       </c>
       <c r="K39" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K40" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>243</v>
+        <v>148</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K41" s="3">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>247</v>
+        <v>148</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3805,7 +3769,7 @@
         <v>248</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
@@ -3814,45 +3778,45 @@
         <v>249</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>92</v>
+        <v>253</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3">
         <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>254</v>
+        <v>65</v>
       </c>
       <c r="K43" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3860,45 +3824,45 @@
         <v>255</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="3">
+        <v>12</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="3">
-        <v>13</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="K44" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>26</v>
@@ -3907,103 +3871,103 @@
         <v>12</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K45" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>60</v>
+        <v>261</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" s="3">
-        <v>12</v>
-      </c>
-      <c r="F46" s="3" t="s">
+      <c r="G46" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="J46" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K46" s="3">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>65</v>
+        <v>271</v>
       </c>
       <c r="K47" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>271</v>
+        <v>62</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -4012,33 +3976,33 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>59</v>
+        <v>181</v>
       </c>
       <c r="K48" s="3">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>274</v>
+        <v>239</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>275</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4047,33 +4011,33 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" s="3" t="s">
+      <c r="J49" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>278</v>
-      </c>
       <c r="K49" s="3">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4082,138 +4046,138 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>282</v>
+        <v>59</v>
       </c>
       <c r="K50" s="3">
-        <v>28</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="3">
+        <v>6</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="3">
-        <v>10</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="K51" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>72</v>
+        <v>285</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="3">
-        <v>10</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K52" s="3">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>6</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="G53" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
-        <v>10</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="J53" s="3" t="s">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="K53" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>245</v>
+        <v>294</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>295</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4222,10 +4186,10 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
@@ -4234,21 +4198,21 @@
         <v>296</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="K54" s="3">
-        <v>43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>299</v>
-      </c>
       <c r="C55" s="3" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4257,103 +4221,103 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>301</v>
-      </c>
       <c r="J55" s="3" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="K55" s="3">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>233</v>
+        <v>94</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="K56" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E57" s="3">
         <v>4</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="K57" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>310</v>
+        <v>148</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>26</v>
@@ -4365,19 +4329,19 @@
         <v>311</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>312</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>65</v>
+        <v>224</v>
       </c>
       <c r="K58" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -4388,112 +4352,112 @@
         <v>314</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>316</v>
+        <v>71</v>
       </c>
       <c r="K59" s="3">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>267</v>
+        <v>313</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>318</v>
+        <v>62</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="J60" s="3" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="K60" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E61" s="3">
-        <v>4</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>65</v>
       </c>
       <c r="K61" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>318</v>
+        <v>143</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4502,33 +4466,33 @@
         <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>65</v>
+        <v>132</v>
       </c>
       <c r="K62" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>131</v>
+        <v>306</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4537,33 +4501,33 @@
         <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="K63" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>333</v>
+        <v>194</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>217</v>
+        <v>330</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4572,164 +4536,26 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>215</v>
+        <v>59</v>
       </c>
       <c r="K64" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E65" s="3">
-        <v>3</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="K65" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" s="3">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K66" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="3">
-        <v>3</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="J67" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="K67" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="3">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K68" s="3">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K68"/>
+  <autoFilter ref="A1:K64"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4794,10 +4620,6 @@
     <hyperlink ref="I62" r:id="rId61"/>
     <hyperlink ref="I63" r:id="rId62"/>
     <hyperlink ref="I64" r:id="rId63"/>
-    <hyperlink ref="I65" r:id="rId64"/>
-    <hyperlink ref="I66" r:id="rId65"/>
-    <hyperlink ref="I67" r:id="rId66"/>
-    <hyperlink ref="I68" r:id="rId67"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4805,8 +4627,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4828,10 +4650,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4839,102 +4661,102 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>188</v>
+        <v>241</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>245</v>
+        <v>194</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -4943,59 +4765,59 @@
         <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>294</v>
+        <v>254</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>122</v>
+        <v>321</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -5022,178 +4844,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B3" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="B4" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B5" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>353</v>
+        <v>316</v>
       </c>
       <c r="B6" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>239</v>
+        <v>341</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="B8" s="3">
         <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="B9" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B11" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -5213,10 +5035,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2">
@@ -5224,10 +5046,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3">
@@ -5235,10 +5057,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4">
@@ -5246,10 +5068,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5">
@@ -5257,10 +5079,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6">
@@ -5268,10 +5090,10 @@
         <v>29</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -5292,13 +5114,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -5306,10 +5128,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5318,22 +5140,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W30.xlsx
+++ b/reports/devops-juniors-israel-2026-W30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-22T08:42:43</t>
+    <t xml:space="preserve">2026-07-23T08:44:27</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -115,6 +115,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rank</t>
   </si>
   <si>
@@ -196,607 +199,739 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
+    <t xml:space="preserve">System Administrator - Linux, Windows #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-linux-windows-%231350-at-rad-4443763825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MER Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4440152008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4443827049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4442985724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-cato-networks-4421931930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer, Software Development, Graviton Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4443042450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communications System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Terraform/IaC, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communications-system-engineer-at-weizmann-institute-of-science-4431070422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enterprise IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nymbus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacksonville, Jacksonville, Florida, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-enterprise-it-support-specialist-nymbus-1135194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-iai-israel-aerospace-industries-4399105085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MER Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-mer-group-4436525380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiberias, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4440132141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-Level NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-level-noc-operator-at-log-on-software-4443136772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414157765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Tier 2 - 240769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-240769-at-experis-israel-4434811963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salvador Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/customer-support-engineer-at-salvador-technologies-4440494256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiberias, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NLPearl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-nlpearl-4440427593</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer - Tier 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Customer Support Rep- Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-customer-support-rep-student-at-bright-data-4440677972</t>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
   </si>
   <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4417221824</t>
   </si>
   <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
@@ -820,9 +955,6 @@
     <t xml:space="preserve">SISL Global</t>
   </si>
   <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
   </si>
   <si>
@@ -859,7 +991,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk</t>
+    <t xml:space="preserve">Help Desk IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umpisa Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasig, Pasig, National Capital Region, Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-help-desk-it-support-specialist-umpisa-inc-1135223</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory, Troubleshooting</t>
@@ -883,21 +1024,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
-  </si>
-  <si>
     <t xml:space="preserve">Field IT Support Specialist</t>
   </si>
   <si>
@@ -907,18 +1033,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
   </si>
   <si>
-    <t xml:space="preserve">תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StoreNext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
-  </si>
-  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -928,133 +1042,160 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
   </si>
   <si>
-    <t xml:space="preserve">Business Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-philips-4433612673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4443762238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-genie-4438491899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔥 בודקי תוכנה מתחילים? – משרה מלאה בדרום הארץ לפניכם!🔥7529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesnet Group Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%F0%9F%94%A5-%D7%91%D7%95%D7%93%D7%A7%D7%99-%D7%AA%D7%95%D7%9B%D7%A0%D7%94-%D7%9E%D7%AA%D7%97%D7%99%D7%9C%D7%99%D7%9D%3F-%E2%80%93-%D7%9E%D7%A9%D7%A8%D7%94-%D7%9E%D7%9C%D7%90%D7%94-%D7%91%D7%93%D7%A8%D7%95%D7%9D-%D7%94%D7%90%D7%A8%D7%A5-%D7%9C%D7%A4%D7%A0%D7%99%D7%9B%D7%9D%21%F0%9F%94%A57529-at-tesnet-group-ltd-4442592044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Placement Officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GoRegional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dehradun,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-placement-officer-goregional-1135232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accel Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-accel-solutions-4439663778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4443762238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -1063,12 +1204,6 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
@@ -1081,15 +1216,15 @@
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -1121,9 +1256,6 @@
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1380,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -1256,7 +1388,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1264,7 +1396,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -1272,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>519</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10">
@@ -1354,7 +1486,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -1362,7 +1494,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -1370,7 +1502,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1404,7 +1536,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -1412,7 +1544,15 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>8</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1436,34 +1576,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1471,13 +1611,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>29</v>
@@ -1486,16 +1626,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1503,13 +1643,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>28</v>
@@ -1518,16 +1658,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1535,13 +1675,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1550,16 +1690,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1567,31 +1707,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1599,13 +1739,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
@@ -1614,16 +1754,16 @@
         <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1631,13 +1771,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -1646,16 +1786,16 @@
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1663,13 +1803,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1678,16 +1818,16 @@
         <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1695,13 +1835,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1710,16 +1850,16 @@
         <v>70</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1727,13 +1867,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1742,16 +1882,16 @@
         <v>68</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1759,7 +1899,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>93</v>
@@ -1771,19 +1911,19 @@
         <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -1800,16 +1940,16 @@
         <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>101</v>
@@ -1823,31 +1963,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -1855,31 +1995,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3">
+        <v>57</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3">
-        <v>52</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -1887,31 +2027,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>56</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>47</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -1919,31 +2059,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1951,19 +2091,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>125</v>
@@ -1989,13 +2129,13 @@
         <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>130</v>
@@ -2021,25 +2161,25 @@
         <v>134</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20">
@@ -2047,31 +2187,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
@@ -2079,31 +2219,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22">
@@ -2111,31 +2251,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="3">
+        <v>44</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
@@ -2143,31 +2283,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24">
@@ -2175,31 +2315,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25">
@@ -2207,19 +2347,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>164</v>
@@ -2239,31 +2379,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2316,48 +2456,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>29</v>
@@ -2366,33 +2506,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>28</v>
@@ -2401,33 +2541,33 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2436,54 +2576,54 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -2491,13 +2631,13 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
@@ -2506,33 +2646,33 @@
         <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>26</v>
@@ -2541,33 +2681,33 @@
         <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2576,33 +2716,33 @@
         <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2611,33 +2751,33 @@
         <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2646,27 +2786,27 @@
         <v>68</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K10" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>93</v>
@@ -2678,22 +2818,22 @@
         <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K11" s="3">
         <v>0</v>
@@ -2710,19 +2850,19 @@
         <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>101</v>
@@ -2731,170 +2871,170 @@
         <v>102</v>
       </c>
       <c r="K12" s="3">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="K13" s="3">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3">
+        <v>57</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="3">
-        <v>52</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="K14" s="3">
-        <v>22</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3">
+        <v>56</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>47</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="K15" s="3">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="K16" s="3">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>125</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
@@ -2906,7 +3046,7 @@
         <v>127</v>
       </c>
       <c r="K17" s="3">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -2917,19 +3057,19 @@
         <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
@@ -2941,7 +3081,7 @@
         <v>132</v>
       </c>
       <c r="K18" s="3">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
@@ -2952,229 +3092,229 @@
         <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="K19" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="K20" s="3">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K21" s="3">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="3">
+        <v>44</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="K22" s="3">
-        <v>22</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K23" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="K24" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>164</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
@@ -3186,39 +3326,39 @@
         <v>166</v>
       </c>
       <c r="K25" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="K26" s="3">
         <v>3</v>
@@ -3226,69 +3366,69 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="3">
+        <v>32</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>27</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="K27" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>32</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>27</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -3296,25 +3436,25 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
@@ -3323,173 +3463,173 @@
         <v>188</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="K29" s="3">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K30" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3">
-        <v>63</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K32" s="3">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="K33" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>211</v>
+        <v>63</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>212</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
@@ -3498,42 +3638,42 @@
         <v>213</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>127</v>
+        <v>214</v>
       </c>
       <c r="K34" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>215</v>
+        <v>62</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="3">
+        <v>27</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="3">
-        <v>20</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="K35" s="3">
         <v>2</v>
@@ -3541,244 +3681,244 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>24</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>17</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>224</v>
+        <v>111</v>
       </c>
       <c r="K36" s="3">
-        <v>8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>166</v>
+        <v>226</v>
       </c>
       <c r="K37" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>61</v>
+        <v>228</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="K38" s="3">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>20</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="3">
-        <v>13</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="G39" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="K39" s="3">
-        <v>14</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F40" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>243</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>148</v>
+        <v>244</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K41" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>148</v>
+        <v>249</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E42" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K42" s="3">
         <v>13</v>
@@ -3786,34 +3926,34 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>253</v>
+        <v>135</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3821,244 +3961,244 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>67</v>
+        <v>258</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>71</v>
+        <v>262</v>
       </c>
       <c r="K44" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="3">
+        <v>17</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E45" s="3">
-        <v>12</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="K45" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>59</v>
+        <v>195</v>
       </c>
       <c r="K46" s="3">
-        <v>59</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>268</v>
+        <v>104</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>271</v>
+        <v>117</v>
       </c>
       <c r="K47" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>62</v>
+        <v>277</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>181</v>
+        <v>66</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="K49" s="3">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>77</v>
+        <v>286</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>278</v>
+        <v>154</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>79</v>
+        <v>155</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="K50" s="3">
         <v>59</v>
@@ -4066,384 +4206,384 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>61</v>
+        <v>289</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>62</v>
+        <v>259</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>284</v>
+        <v>102</v>
       </c>
       <c r="K51" s="3">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>143</v>
+        <v>294</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="K52" s="3">
-        <v>52</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>291</v>
+        <v>119</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="K53" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>295</v>
+        <v>154</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>221</v>
+        <v>301</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="K54" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>298</v>
+        <v>154</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>221</v>
+        <v>155</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E55" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="K55" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>93</v>
+        <v>307</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>94</v>
+        <v>308</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>232</v>
+        <v>60</v>
       </c>
       <c r="K56" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>306</v>
+        <v>114</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>71</v>
+        <v>315</v>
       </c>
       <c r="K57" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>224</v>
+        <v>88</v>
       </c>
       <c r="K58" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>315</v>
+        <v>80</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>71</v>
+        <v>321</v>
       </c>
       <c r="K59" s="3">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="K60" s="3">
-        <v>9</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>148</v>
+        <v>327</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4451,111 +4591,492 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>323</v>
+        <v>263</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>324</v>
+        <v>219</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>132</v>
+        <v>331</v>
       </c>
       <c r="K62" s="3">
-        <v>9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>306</v>
+        <v>144</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="K63" s="3">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>194</v>
+        <v>336</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E64" s="3">
+        <v>6</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K64" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="3">
+        <v>4</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K65" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K66" s="3">
         <v>3</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="K64" s="3">
-        <v>59</v>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" s="3">
+        <v>4</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K67" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K68" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K69" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K70" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K71" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="K72" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K73" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" s="3">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K75" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K64"/>
+  <autoFilter ref="A1:K75"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4620,6 +5141,17 @@
     <hyperlink ref="I62" r:id="rId61"/>
     <hyperlink ref="I63" r:id="rId62"/>
     <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
+    <hyperlink ref="I71" r:id="rId70"/>
+    <hyperlink ref="I72" r:id="rId71"/>
+    <hyperlink ref="I73" r:id="rId72"/>
+    <hyperlink ref="I74" r:id="rId73"/>
+    <hyperlink ref="I75" r:id="rId74"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4627,7 +5159,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -4638,53 +5170,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>93</v>
@@ -4693,7 +5225,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>95</v>
@@ -4702,126 +5234,237 @@
         <v>96</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>67</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>186</v>
+        <v>106</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>239</v>
+        <v>118</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>241</v>
+        <v>120</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>242</v>
+        <v>121</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>243</v>
+        <v>180</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>245</v>
+        <v>183</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>251</v>
+        <v>205</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>252</v>
+        <v>206</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>320</v>
+        <v>253</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>321</v>
+        <v>254</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>322</v>
+        <v>256</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>17</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="3">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G13"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4830,6 +5473,11 @@
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
+    <hyperlink ref="F11" r:id="rId10"/>
+    <hyperlink ref="F12" r:id="rId11"/>
+    <hyperlink ref="F13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4844,178 +5492,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>379</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>334</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>335</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>336</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>302</v>
+        <v>384</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>339</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>316</v>
+        <v>344</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>340</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>341</v>
+        <v>387</v>
       </c>
       <c r="B7" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>342</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>344</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>345</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>236</v>
+        <v>391</v>
       </c>
       <c r="B10" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>346</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>348</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>349</v>
+        <v>394</v>
       </c>
       <c r="B12" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>350</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>351</v>
+        <v>396</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>352</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>353</v>
+        <v>398</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>354</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>356</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>350</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -5032,13 +5680,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>359</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2">
@@ -5046,10 +5694,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3">
@@ -5057,10 +5705,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4">
@@ -5068,10 +5716,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>362</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5">
@@ -5082,7 +5730,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>363</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6">
@@ -5093,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>364</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -5111,16 +5759,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>366</v>
+        <v>411</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>367</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2">
@@ -5128,10 +5776,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>368</v>
+        <v>413</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5140,22 +5788,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>368</v>
+        <v>413</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>369</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>368</v>
+        <v>413</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W30.xlsx
+++ b/reports/devops-juniors-israel-2026-W30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="430">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-23T08:44:27</t>
+    <t xml:space="preserve">2026-07-24T08:40:12</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -217,6 +217,24 @@
     <t xml:space="preserve">2026-07-23</t>
   </si>
   <si>
+    <t xml:space="preserve">Test Environment Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
@@ -283,6 +301,15 @@
     <t xml:space="preserve">2026-07-21</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anecdotes</t>
   </si>
   <si>
@@ -295,810 +322,849 @@
     <t xml:space="preserve">2026-06-18</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantHealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-quanthealth-4444080917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-at-align-technology-4441786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2 - 240769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-240769-at-experis-israel-4434811963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enterprise IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nymbus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacksonville, Jacksonville, Florida, United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-enterprise-it-support-specialist-nymbus-1135194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helpdesk Specialist טכנאי/ת תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAT Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Gat, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-specialist-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-tat-technologies-ltd-4441048130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiberias, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4431915164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4440132141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid-Level NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-level-noc-operator-at-log-on-software-4443136772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Customer Support Rep- Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-customer-support-rep-student-at-bright-data-4440677972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4440113168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4417221824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-sela-4441038419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umpisa Inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasig, Pasig, National Capital Region, Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-help-desk-it-support-specialist-umpisa-inc-1135223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37062-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4444411920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoreNext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Confidential</t>
   </si>
   <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Terraform/IaC, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-confidential-4443827049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4442985724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-cato-networks-4421931930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer, Software Development, Graviton Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-software-development-graviton-team-at-amazon-web-services-aws-4443042450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finonex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-zyg-4441776623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communications System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Terraform/IaC, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communications-system-engineer-at-weizmann-institute-of-science-4431070422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELP DESK TIER TWO 241758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-two-241758-at-experis-4439208565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-philips-4433612673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enterprise IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nymbus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacksonville, Jacksonville, Florida, United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-enterprise-it-support-specialist-nymbus-1135194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4442592331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-specialist-at-silverfort-4434301874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magal, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת סיסטם בכיר/ה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiberias, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%A1%D7%99%D7%A1%D7%98%D7%9D-%D7%91%D7%9B%D7%99%D7%A8-%D7%94-at-genie-4438484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4440132141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForSight Robotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid-Level NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mid-level-noc-operator-at-log-on-software-4443136772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-elbit-systems-israel-4385022682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-elbit-systems-israel-4417221824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician (36735)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-36735-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4442595551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umpisa Inc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasig, Pasig, National Capital Region, Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-help-desk-it-support-specialist-umpisa-inc-1135223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4425017778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tnuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uvision Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4440955157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-at-philips-4433612673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
   </si>
   <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4443762238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Support Technician (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-student-position-at-log-on-software-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk טכנאי/ת</t>
   </si>
   <si>
@@ -1108,24 +1174,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-genie-4438491899</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4442521601</t>
-  </si>
-  <si>
     <t xml:space="preserve">🔥 בודקי תוכנה מתחילים? – משרה מלאה בדרום הארץ לפניכם!🔥7529</t>
   </si>
   <si>
@@ -1138,6 +1186,12 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/%F0%9F%94%A5-%D7%91%D7%95%D7%93%D7%A7%D7%99-%D7%AA%D7%95%D7%9B%D7%A0%D7%94-%D7%9E%D7%AA%D7%97%D7%99%D7%9C%D7%99%D7%9D%3F-%E2%80%93-%D7%9E%D7%A9%D7%A8%D7%94-%D7%9E%D7%9C%D7%90%D7%94-%D7%91%D7%93%D7%A8%D7%95%D7%9D-%D7%94%D7%90%D7%A8%D7%A5-%D7%9C%D7%A4%D7%A0%D7%99%D7%9B%D7%9D%21%F0%9F%94%A57529-at-tesnet-group-ltd-4442592044</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
     <t xml:space="preserve">Student Placement Officer</t>
   </si>
   <si>
@@ -1159,15 +1213,18 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -1177,6 +1234,9 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
@@ -1186,30 +1246,24 @@
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
@@ -1217,12 +1271,6 @@
   </si>
   <si>
     <t xml:space="preserve">Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1380,7 +1428,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -1388,7 +1436,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1396,7 +1444,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -1404,7 +1452,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10">
@@ -1486,7 +1534,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -1494,7 +1542,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -1502,7 +1550,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -1536,7 +1584,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
@@ -1748,10 +1796,10 @@
         <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>70</v>
@@ -1771,13 +1819,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -1786,16 +1834,16 @@
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1803,7 +1851,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>79</v>
@@ -1812,10 +1860,10 @@
         <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>81</v>
@@ -1841,25 +1889,25 @@
         <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1867,31 +1915,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -1899,22 +1947,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
@@ -1923,7 +1971,7 @@
         <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1931,31 +1979,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3">
-        <v>60</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -1963,7 +2011,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>103</v>
@@ -1981,13 +2029,13 @@
         <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -2001,7 +2049,7 @@
         <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>28</v>
@@ -2065,25 +2113,25 @@
         <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -2091,13 +2139,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
@@ -2106,16 +2154,16 @@
         <v>52</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
@@ -2123,31 +2171,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19">
@@ -2161,25 +2209,25 @@
         <v>134</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="20">
@@ -2187,31 +2235,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -2219,19 +2267,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>145</v>
@@ -2257,19 +2305,19 @@
         <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>150</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>151</v>
@@ -2283,31 +2331,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>34</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="3">
-        <v>40</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
@@ -2315,31 +2363,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="3">
+        <v>32</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>37</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25">
@@ -2347,31 +2395,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3">
+        <v>32</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>34</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26">
@@ -2379,31 +2427,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2521,7 +2569,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -2556,7 +2604,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
@@ -2591,7 +2639,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -2626,7 +2674,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2640,10 +2688,10 @@
         <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>70</v>
@@ -2661,18 +2709,18 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>26</v>
@@ -2681,7 +2729,7 @@
         <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>175</v>
@@ -2690,18 +2738,18 @@
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>79</v>
@@ -2710,10 +2758,10 @@
         <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>81</v>
@@ -2731,7 +2779,7 @@
         <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2742,16 +2790,16 @@
         <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>175</v>
@@ -2760,33 +2808,33 @@
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>175</v>
@@ -2795,33 +2843,33 @@
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K10" s="3">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>175</v>
@@ -2833,50 +2881,50 @@
         <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>68</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="3">
-        <v>60</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="K12" s="3">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>103</v>
@@ -2897,16 +2945,16 @@
         <v>175</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2917,7 +2965,7 @@
         <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>28</v>
@@ -2941,7 +2989,7 @@
         <v>111</v>
       </c>
       <c r="K14" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -2976,7 +3024,7 @@
         <v>117</v>
       </c>
       <c r="K15" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -2987,16 +3035,16 @@
         <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>175</v>
@@ -3005,24 +3053,24 @@
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
@@ -3031,7 +3079,7 @@
         <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>175</v>
@@ -3040,48 +3088,48 @@
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K17" s="3">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="K18" s="3">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
@@ -3092,83 +3140,83 @@
         <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>52</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="K19" s="3">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="K20" s="3">
-        <v>69</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>145</v>
@@ -3186,7 +3234,7 @@
         <v>147</v>
       </c>
       <c r="K21" s="3">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3197,13 +3245,13 @@
         <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>150</v>
@@ -3212,7 +3260,7 @@
         <v>175</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>151</v>
@@ -3221,167 +3269,167 @@
         <v>152</v>
       </c>
       <c r="K22" s="3">
-        <v>65</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>34</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="3">
-        <v>40</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="K23" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="3">
+        <v>32</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>37</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="K24" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="3">
+        <v>32</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>34</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="K25" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K26" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>67</v>
+        <v>176</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>175</v>
@@ -3390,33 +3438,33 @@
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="K27" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>175</v>
@@ -3425,24 +3473,24 @@
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>186</v>
+        <v>69</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3451,7 +3499,7 @@
         <v>30</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>175</v>
@@ -3460,13 +3508,13 @@
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="K29" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -3492,118 +3540,118 @@
         <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="K30" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="3">
+        <v>28</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>30</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="K31" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>24</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>30</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="K32" s="3">
-        <v>29</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -3611,54 +3659,54 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3">
+        <v>23</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="3">
-        <v>28</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="K34" s="3">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>216</v>
@@ -3673,65 +3721,65 @@
         <v>217</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>88</v>
+        <v>218</v>
       </c>
       <c r="K35" s="3">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>104</v>
+        <v>221</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>111</v>
       </c>
       <c r="K36" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>80</v>
+        <v>226</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>175</v>
@@ -3740,33 +3788,33 @@
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="K37" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>144</v>
+        <v>231</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>175</v>
@@ -3775,68 +3823,68 @@
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K38" s="3">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E39" s="3">
         <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="K39" s="3">
-        <v>69</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>238</v>
+        <v>139</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>239</v>
+        <v>140</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E40" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>175</v>
@@ -3845,33 +3893,33 @@
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="K40" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>175</v>
@@ -3880,30 +3928,30 @@
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K41" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>249</v>
+        <v>158</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>250</v>
@@ -3921,7 +3969,7 @@
         <v>252</v>
       </c>
       <c r="K42" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -3932,7 +3980,7 @@
         <v>254</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>135</v>
+        <v>255</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3941,7 +3989,7 @@
         <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>175</v>
@@ -3953,10 +4001,10 @@
         <v>256</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>66</v>
+        <v>169</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -3964,10 +4012,10 @@
         <v>257</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>258</v>
+        <v>68</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>259</v>
+        <v>69</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3976,7 +4024,7 @@
         <v>17</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>175</v>
@@ -3985,24 +4033,24 @@
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>262</v>
+        <v>117</v>
       </c>
       <c r="K44" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -4011,7 +4059,7 @@
         <v>17</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>175</v>
@@ -4020,65 +4068,65 @@
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>66</v>
       </c>
       <c r="K45" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="3">
+        <v>16</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="G46" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" s="3">
-        <v>17</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="J46" s="3" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="K46" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E47" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>273</v>
@@ -4087,62 +4135,62 @@
         <v>175</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>274</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>117</v>
+        <v>275</v>
       </c>
       <c r="K47" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>276</v>
+        <v>139</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>277</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E48" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F48" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>279</v>
-      </c>
       <c r="J48" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>281</v>
+        <v>139</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>282</v>
+        <v>140</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>27</v>
@@ -4151,42 +4199,42 @@
         <v>13</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="K49" s="3">
-        <v>15</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>154</v>
+        <v>283</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E50" s="3">
         <v>13</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>175</v>
@@ -4195,24 +4243,24 @@
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="K50" s="3">
-        <v>59</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>259</v>
+        <v>63</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4221,7 +4269,7 @@
         <v>13</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>175</v>
@@ -4230,33 +4278,33 @@
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="K51" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E52" s="3">
         <v>13</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>175</v>
@@ -4265,33 +4313,33 @@
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>297</v>
+        <v>72</v>
       </c>
       <c r="K52" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E53" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>175</v>
@@ -4300,24 +4348,24 @@
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="K53" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>67</v>
+        <v>296</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>26</v>
@@ -4326,7 +4374,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>175</v>
@@ -4335,24 +4383,24 @@
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>72</v>
+        <v>275</v>
       </c>
       <c r="K54" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>304</v>
+        <v>73</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>155</v>
+        <v>300</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>26</v>
@@ -4361,7 +4409,7 @@
         <v>12</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>175</v>
@@ -4370,59 +4418,59 @@
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K55" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>307</v>
+        <v>139</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>308</v>
+        <v>140</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E56" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K56" s="3">
-        <v>60</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>114</v>
+        <v>306</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4431,33 +4479,33 @@
         <v>10</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>315</v>
+        <v>60</v>
       </c>
       <c r="K57" s="3">
-        <v>6</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>316</v>
+        <v>213</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
@@ -4466,7 +4514,7 @@
         <v>10</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>175</v>
@@ -4475,24 +4523,24 @@
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
       <c r="K58" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
@@ -4510,24 +4558,24 @@
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="K59" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4536,7 +4584,7 @@
         <v>10</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>175</v>
@@ -4545,24 +4593,24 @@
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>60</v>
+        <v>318</v>
       </c>
       <c r="K60" s="3">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>327</v>
+        <v>63</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4577,36 +4625,36 @@
         <v>175</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>66</v>
+        <v>322</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>219</v>
+        <v>323</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>175</v>
@@ -4615,68 +4663,68 @@
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>331</v>
+        <v>60</v>
       </c>
       <c r="K62" s="3">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>144</v>
+        <v>328</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="K63" s="3">
-        <v>53</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>337</v>
+        <v>139</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E64" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>175</v>
@@ -4685,68 +4733,68 @@
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>83</v>
+        <v>199</v>
       </c>
       <c r="K64" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>98</v>
+        <v>334</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="K65" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>342</v>
+        <v>68</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>343</v>
+        <v>69</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E66" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>175</v>
@@ -4755,33 +4803,33 @@
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>72</v>
+        <v>281</v>
       </c>
       <c r="K66" s="3">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E67" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>175</v>
@@ -4790,33 +4838,33 @@
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>72</v>
+        <v>343</v>
       </c>
       <c r="K67" s="3">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E68" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>175</v>
@@ -4825,103 +4873,103 @@
         <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>200</v>
+        <v>89</v>
       </c>
       <c r="K68" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>355</v>
+        <v>103</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E69" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="K69" s="3">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>104</v>
+        <v>353</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E70" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="J70" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="K70" s="3">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>243</v>
+        <v>358</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E71" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>175</v>
@@ -4930,153 +4978,361 @@
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="K71" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>367</v>
-      </c>
       <c r="J72" s="3" t="s">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="K72" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>201</v>
+        <v>365</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" s="3">
+        <v>4</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="3">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>369</v>
-      </c>
       <c r="J73" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K73" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I74" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="J74" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E74" s="3">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K74" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E75" s="3">
+        <v>3</v>
+      </c>
+      <c r="F75" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="G75" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="J75" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="K75" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="K76" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="3">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K77" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="3">
+        <v>3</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K78" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E79" s="3">
         <v>0</v>
       </c>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H75" s="3" t="s">
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K79" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E80" s="3">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K80" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I75" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="J75" s="3" t="s">
+      <c r="I81" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="J81" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="K75" s="3">
-        <v>0</v>
+      <c r="K81" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K75"/>
+  <autoFilter ref="A1:K81"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5152,6 +5408,12 @@
     <hyperlink ref="I73" r:id="rId72"/>
     <hyperlink ref="I74" r:id="rId73"/>
     <hyperlink ref="I75" r:id="rId74"/>
+    <hyperlink ref="I76" r:id="rId75"/>
+    <hyperlink ref="I77" r:id="rId76"/>
+    <hyperlink ref="I78" r:id="rId77"/>
+    <hyperlink ref="I79" r:id="rId78"/>
+    <hyperlink ref="I80" r:id="rId79"/>
+    <hyperlink ref="I81" r:id="rId80"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5159,9 +5421,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5193,291 +5455,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>67</v>
+        <v>203</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>118</v>
+        <v>213</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>119</v>
+        <v>309</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>120</v>
+        <v>298</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>121</v>
+        <v>310</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>179</v>
+        <v>333</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>180</v>
+        <v>334</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>182</v>
+        <v>335</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>183</v>
+        <v>336</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>30</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>17</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3">
-        <v>17</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="3">
-        <v>16</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>10</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>66</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
-    <hyperlink ref="F13" r:id="rId12"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5492,178 +5590,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B2" s="3">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B4" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>384</v>
+        <v>273</v>
       </c>
       <c r="B5" s="3">
         <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>344</v>
+        <v>403</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="B7" s="3">
         <v>23</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>283</v>
+        <v>407</v>
       </c>
       <c r="B9" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B10" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>362</v>
+        <v>298</v>
       </c>
       <c r="B11" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B12" s="3">
         <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="B13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="B16" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -5683,10 +5781,10 @@
         <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2">
@@ -5694,10 +5792,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3">
@@ -5705,10 +5803,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4">
@@ -5716,10 +5814,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5">
@@ -5730,7 +5828,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6">
@@ -5741,7 +5839,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -5762,13 +5860,13 @@
         <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2">
@@ -5779,7 +5877,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5788,10 +5886,10 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5803,7 +5901,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="D4" s="3"/>
     </row>
